--- a/schema/tots/ag/harvest/yield-moisture/year-index/2026/field-index/north80.schema/schema.xlsx
+++ b/schema/tots/ag/harvest/yield-moisture/year-index/2026/field-index/north80.schema/schema.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:S3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -441,18 +441,21 @@
         <v>rowTypeSet</v>
       </c>
       <c r="N1" t="str">
+        <v>additionalProperties</v>
+      </c>
+      <c r="O1" t="str">
         <v>startCell</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>endCell</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>orientation</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>payloadFormat</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>notes</v>
       </c>
     </row>
@@ -511,6 +514,9 @@
       <c r="R2" t="str">
         <v/>
       </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -567,10 +573,13 @@
       <c r="R3" t="str">
         <v/>
       </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S3"/>
   </ignoredErrors>
 </worksheet>
 </file>
